--- a/artfynd/A 29249-2024 artfynd.xlsx
+++ b/artfynd/A 29249-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118392681</v>
+        <v>118394124</v>
       </c>
       <c r="B2" t="n">
         <v>57290</v>
@@ -711,19 +711,19 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585521</v>
+        <v>585688</v>
       </c>
       <c r="R2" t="n">
-        <v>7059734</v>
+        <v>7059736</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,19 +753,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:21</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,19 +770,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118393140</v>
+        <v>118392681</v>
       </c>
       <c r="B3" t="n">
         <v>57290</v>
@@ -828,19 +818,19 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585675</v>
+        <v>585521</v>
       </c>
       <c r="R3" t="n">
-        <v>7059730</v>
+        <v>7059734</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118393098</v>
+        <v>118393091</v>
       </c>
       <c r="B4" t="n">
-        <v>57290</v>
+        <v>90500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585670</v>
+        <v>585652</v>
       </c>
       <c r="R4" t="n">
-        <v>7059736</v>
+        <v>7059750</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,19 +999,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118392662</v>
+        <v>118392747</v>
       </c>
       <c r="B5" t="n">
         <v>57290</v>
@@ -1071,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585511</v>
+        <v>585537</v>
       </c>
       <c r="R5" t="n">
-        <v>7059745</v>
+        <v>7059747</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,7 +1128,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118394124</v>
+        <v>118393140</v>
       </c>
       <c r="B6" t="n">
         <v>57290</v>
@@ -1188,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585688</v>
+        <v>585675</v>
       </c>
       <c r="R6" t="n">
-        <v>7059736</v>
+        <v>7059730</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,9 +1206,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,22 +1233,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118393553</v>
+        <v>118393105</v>
       </c>
       <c r="B7" t="n">
-        <v>57290</v>
+        <v>57443</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,42 +1261,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget (Rågsvedjeberget), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585834</v>
+        <v>585652</v>
       </c>
       <c r="R7" t="n">
-        <v>7059529</v>
+        <v>7059750</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,22 +1350,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118393105</v>
+        <v>118393553</v>
       </c>
       <c r="B8" t="n">
-        <v>57443</v>
+        <v>57290</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,42 +1378,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Rågsvedjeberget (Rågsvedjeberget), Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585652</v>
+        <v>585834</v>
       </c>
       <c r="R8" t="n">
-        <v>7059750</v>
+        <v>7059529</v>
       </c>
       <c r="S8" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,19 +1467,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118392747</v>
+        <v>118392662</v>
       </c>
       <c r="B9" t="n">
         <v>57290</v>
@@ -1529,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585537</v>
+        <v>585511</v>
       </c>
       <c r="R9" t="n">
-        <v>7059747</v>
+        <v>7059745</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118392104</v>
+        <v>118393098</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,45 +1608,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585410</v>
+        <v>585670</v>
       </c>
       <c r="R10" t="n">
-        <v>7059885</v>
+        <v>7059736</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1680,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,7 +1686,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,22 +1701,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118393091</v>
+        <v>118392104</v>
       </c>
       <c r="B11" t="n">
-        <v>90500</v>
+        <v>97846</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,41 +1725,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585652</v>
+        <v>585410</v>
       </c>
       <c r="R11" t="n">
-        <v>7059750</v>
+        <v>7059885</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 29249-2024 artfynd.xlsx
+++ b/artfynd/A 29249-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118394124</v>
+        <v>118392104</v>
       </c>
       <c r="B2" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585688</v>
+        <v>585410</v>
       </c>
       <c r="R2" t="n">
-        <v>7059736</v>
+        <v>7059885</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,9 +752,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118392681</v>
+        <v>118392747</v>
       </c>
       <c r="B3" t="n">
         <v>57290</v>
@@ -818,7 +827,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -827,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585521</v>
+        <v>585537</v>
       </c>
       <c r="R3" t="n">
-        <v>7059734</v>
+        <v>7059747</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118393091</v>
+        <v>118392681</v>
       </c>
       <c r="B4" t="n">
-        <v>90500</v>
+        <v>57290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +924,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585652</v>
+        <v>585521</v>
       </c>
       <c r="R4" t="n">
-        <v>7059750</v>
+        <v>7059734</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +1013,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118392747</v>
+        <v>118393091</v>
       </c>
       <c r="B5" t="n">
-        <v>57290</v>
+        <v>90500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,39 +1041,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585537</v>
+        <v>585652</v>
       </c>
       <c r="R5" t="n">
-        <v>7059747</v>
+        <v>7059750</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1125,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118393140</v>
+        <v>118393105</v>
       </c>
       <c r="B6" t="n">
-        <v>57290</v>
+        <v>57443</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,27 +1153,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1173,13 +1182,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585675</v>
+        <v>585652</v>
       </c>
       <c r="R6" t="n">
-        <v>7059730</v>
+        <v>7059750</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,22 +1242,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118393105</v>
+        <v>118393553</v>
       </c>
       <c r="B7" t="n">
-        <v>57443</v>
+        <v>57290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,42 +1270,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Rågsvedjeberget (Rågsvedjeberget), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585652</v>
+        <v>585834</v>
       </c>
       <c r="R7" t="n">
-        <v>7059750</v>
+        <v>7059529</v>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,19 +1359,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118393553</v>
+        <v>118393098</v>
       </c>
       <c r="B8" t="n">
         <v>57290</v>
@@ -1398,19 +1407,19 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget (Rågsvedjeberget), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585834</v>
+        <v>585670</v>
       </c>
       <c r="R8" t="n">
-        <v>7059529</v>
+        <v>7059736</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,7 +1488,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118392662</v>
+        <v>118394124</v>
       </c>
       <c r="B9" t="n">
         <v>57290</v>
@@ -1520,14 +1529,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585511</v>
+        <v>585688</v>
       </c>
       <c r="R9" t="n">
-        <v>7059745</v>
+        <v>7059736</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,19 +1566,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,19 +1583,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118393098</v>
+        <v>118392662</v>
       </c>
       <c r="B10" t="n">
         <v>57290</v>
@@ -1637,14 +1636,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585670</v>
+        <v>585511</v>
       </c>
       <c r="R10" t="n">
-        <v>7059736</v>
+        <v>7059745</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,7 +1685,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118392104</v>
+        <v>118393140</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,45 +1724,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585410</v>
+        <v>585675</v>
       </c>
       <c r="R11" t="n">
-        <v>7059885</v>
+        <v>7059730</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,12 +1817,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 29249-2024 artfynd.xlsx
+++ b/artfynd/A 29249-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118392104</v>
+        <v>118392747</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585410</v>
+        <v>585537</v>
       </c>
       <c r="R2" t="n">
-        <v>7059885</v>
+        <v>7059747</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,19 +780,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118392747</v>
+        <v>118392662</v>
       </c>
       <c r="B3" t="n">
         <v>57290</v>
@@ -836,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585537</v>
+        <v>585511</v>
       </c>
       <c r="R3" t="n">
-        <v>7059747</v>
+        <v>7059745</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118392681</v>
+        <v>118393098</v>
       </c>
       <c r="B4" t="n">
         <v>57290</v>
@@ -944,19 +945,19 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585521</v>
+        <v>585670</v>
       </c>
       <c r="R4" t="n">
-        <v>7059734</v>
+        <v>7059736</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118393091</v>
+        <v>118393140</v>
       </c>
       <c r="B5" t="n">
-        <v>90500</v>
+        <v>57290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,34 +1042,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585652</v>
+        <v>585675</v>
       </c>
       <c r="R5" t="n">
-        <v>7059750</v>
+        <v>7059730</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,22 +1131,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118393105</v>
+        <v>118394124</v>
       </c>
       <c r="B6" t="n">
-        <v>57443</v>
+        <v>57290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,27 +1159,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1182,13 +1188,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585652</v>
+        <v>585688</v>
       </c>
       <c r="R6" t="n">
-        <v>7059750</v>
+        <v>7059736</v>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,19 +1221,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118393553</v>
+        <v>118393091</v>
       </c>
       <c r="B7" t="n">
-        <v>57290</v>
+        <v>90507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,39 +1266,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget (Rågsvedjeberget), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585834</v>
+        <v>585652</v>
       </c>
       <c r="R7" t="n">
-        <v>7059529</v>
+        <v>7059750</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,19 +1350,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118393098</v>
+        <v>118392681</v>
       </c>
       <c r="B8" t="n">
         <v>57290</v>
@@ -1407,19 +1398,19 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585670</v>
+        <v>585521</v>
       </c>
       <c r="R8" t="n">
-        <v>7059736</v>
+        <v>7059734</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118394124</v>
+        <v>118393105</v>
       </c>
       <c r="B9" t="n">
-        <v>57290</v>
+        <v>57443</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,27 +1495,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1533,13 +1524,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585688</v>
+        <v>585652</v>
       </c>
       <c r="R9" t="n">
-        <v>7059736</v>
+        <v>7059750</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1566,9 +1557,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118392662</v>
+        <v>118392104</v>
       </c>
       <c r="B10" t="n">
-        <v>57290</v>
+        <v>97853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,31 +1608,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1640,13 +1640,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585511</v>
+        <v>585410</v>
       </c>
       <c r="R10" t="n">
-        <v>7059745</v>
+        <v>7059885</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,19 +1700,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118393140</v>
+        <v>118393553</v>
       </c>
       <c r="B11" t="n">
         <v>57290</v>
@@ -1748,19 +1748,19 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Rågsvedjeberget (Rågsvedjeberget), Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585675</v>
+        <v>585834</v>
       </c>
       <c r="R11" t="n">
-        <v>7059730</v>
+        <v>7059529</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 29249-2024 artfynd.xlsx
+++ b/artfynd/A 29249-2024 artfynd.xlsx
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118392681</v>
+        <v>118393105</v>
       </c>
       <c r="B8" t="n">
-        <v>57290</v>
+        <v>57443</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,42 +1378,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585521</v>
+        <v>585652</v>
       </c>
       <c r="R8" t="n">
-        <v>7059734</v>
+        <v>7059750</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,22 +1467,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118393105</v>
+        <v>118392104</v>
       </c>
       <c r="B9" t="n">
-        <v>57443</v>
+        <v>97853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,46 +1491,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585652</v>
+        <v>585410</v>
       </c>
       <c r="R9" t="n">
-        <v>7059750</v>
+        <v>7059885</v>
       </c>
       <c r="S9" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1559,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118392104</v>
+        <v>118392681</v>
       </c>
       <c r="B10" t="n">
-        <v>97853</v>
+        <v>57290</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,30 +1607,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1640,13 +1640,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585410</v>
+        <v>585521</v>
       </c>
       <c r="R10" t="n">
-        <v>7059885</v>
+        <v>7059734</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,12 +1700,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 29249-2024 artfynd.xlsx
+++ b/artfynd/A 29249-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118392747</v>
+        <v>118393553</v>
       </c>
       <c r="B2" t="n">
         <v>57290</v>
@@ -711,19 +711,19 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Rågsvedjeberget (Rågsvedjeberget), Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585537</v>
+        <v>585834</v>
       </c>
       <c r="R2" t="n">
-        <v>7059747</v>
+        <v>7059529</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118392662</v>
+        <v>118394124</v>
       </c>
       <c r="B3" t="n">
         <v>57290</v>
@@ -833,14 +833,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Timmeråsen (Timmeråsen), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585511</v>
+        <v>585688</v>
       </c>
       <c r="R3" t="n">
-        <v>7059745</v>
+        <v>7059736</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,19 +870,9 @@
           <t>2024-07-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-07-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,19 +887,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118393098</v>
+        <v>118392681</v>
       </c>
       <c r="B4" t="n">
         <v>57290</v>
@@ -945,19 +935,19 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585670</v>
+        <v>585521</v>
       </c>
       <c r="R4" t="n">
-        <v>7059736</v>
+        <v>7059734</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118393140</v>
+        <v>118392662</v>
       </c>
       <c r="B5" t="n">
         <v>57290</v>
@@ -1067,14 +1057,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
+          <t>Timmeråsen (Timmeråsen), Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585675</v>
+        <v>585511</v>
       </c>
       <c r="R5" t="n">
-        <v>7059730</v>
+        <v>7059745</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118394124</v>
+        <v>118393105</v>
       </c>
       <c r="B6" t="n">
-        <v>57290</v>
+        <v>57443</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,27 +1149,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1188,13 +1178,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585688</v>
+        <v>585652</v>
       </c>
       <c r="R6" t="n">
-        <v>7059736</v>
+        <v>7059750</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,9 +1211,19 @@
           <t>2024-07-12</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118393091</v>
+        <v>118393140</v>
       </c>
       <c r="B7" t="n">
-        <v>90507</v>
+        <v>57290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,34 +1266,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585652</v>
+        <v>585675</v>
       </c>
       <c r="R7" t="n">
-        <v>7059750</v>
+        <v>7059730</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,22 +1355,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118393105</v>
+        <v>118393098</v>
       </c>
       <c r="B8" t="n">
-        <v>57443</v>
+        <v>57290</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,27 +1383,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1407,13 +1412,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585652</v>
+        <v>585670</v>
       </c>
       <c r="R8" t="n">
-        <v>7059750</v>
+        <v>7059736</v>
       </c>
       <c r="S8" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,12 +1472,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1595,7 +1600,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118392681</v>
+        <v>118392747</v>
       </c>
       <c r="B10" t="n">
         <v>57290</v>
@@ -1631,7 +1636,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1640,10 +1645,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585521</v>
+        <v>585537</v>
       </c>
       <c r="R10" t="n">
-        <v>7059734</v>
+        <v>7059747</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1690,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,10 +1717,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118393553</v>
+        <v>118393091</v>
       </c>
       <c r="B11" t="n">
-        <v>57290</v>
+        <v>90507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,39 +1733,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rågsvedjeberget (Rågsvedjeberget), Ång</t>
+          <t>Sör-Tågsjöberget (Sör-Tågsjöberget), Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585834</v>
+        <v>585652</v>
       </c>
       <c r="R11" t="n">
-        <v>7059529</v>
+        <v>7059750</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,12 +1817,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 29249-2024 artfynd.xlsx
+++ b/artfynd/A 29249-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1827,6 +1827,210 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126056932</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80100</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>585566</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7059768</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126057019</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>585525</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7059776</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack,  tall</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29249-2024 artfynd.xlsx
+++ b/artfynd/A 29249-2024 artfynd.xlsx
@@ -1832,7 +1832,7 @@
         <v>126056932</v>
       </c>
       <c r="B12" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29249-2024 artfynd.xlsx
+++ b/artfynd/A 29249-2024 artfynd.xlsx
@@ -1832,7 +1832,7 @@
         <v>126056932</v>
       </c>
       <c r="B12" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>126057019</v>
       </c>
       <c r="B13" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29249-2024 artfynd.xlsx
+++ b/artfynd/A 29249-2024 artfynd.xlsx
@@ -1832,7 +1832,7 @@
         <v>126056932</v>
       </c>
       <c r="B12" t="n">
-        <v>80105</v>
+        <v>80109</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>126057019</v>
       </c>
       <c r="B13" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29249-2024 artfynd.xlsx
+++ b/artfynd/A 29249-2024 artfynd.xlsx
@@ -1832,7 +1832,7 @@
         <v>126056932</v>
       </c>
       <c r="B12" t="n">
-        <v>80109</v>
+        <v>80112</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>126057019</v>
       </c>
       <c r="B13" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
